--- a/Targets.xlsx
+++ b/Targets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ThinkPad\Desktop\Work Flow Planning\October 2026 1.5 M\Dashboard\Final\Updated Version\target test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C419522-3859-4229-A9DC-C066904C74AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3864B60F-852B-4A9C-BCD1-460C7193088C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-975" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Config" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Universities Targets" sheetId="4" r:id="rId4"/>
     <sheet name="Users Target" sheetId="5" r:id="rId5"/>
     <sheet name="Uni Calendar" sheetId="6" r:id="rId6"/>
-    <sheet name="Sheet1" sheetId="8" r:id="rId7"/>
+    <sheet name="Hour Weights" sheetId="8" r:id="rId7"/>
     <sheet name="User Pacing Curve" sheetId="7" r:id="rId8"/>
   </sheets>
   <definedNames>
@@ -758,9 +758,6 @@
     <t>Paste the previous full month of the Users Segments Funnel export here each month. Used only as the shape of how segment users accumulate through a month.</t>
   </si>
   <si>
-    <t>2026-11</t>
-  </si>
-  <si>
     <t>period_morning_start</t>
   </si>
   <si>
@@ -873,6 +870,9 @@
   </si>
   <si>
     <t>avg_trips_per_weekend_day</t>
+  </si>
+  <si>
+    <t>2026-10</t>
   </si>
 </sst>
 </file>
@@ -1438,7 +1438,7 @@
         <v>58</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>209</v>
+        <v>247</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>59</v>
@@ -1567,172 +1567,172 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B14" s="16">
         <v>6</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B15" s="16">
         <v>12</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B16" s="16">
         <v>16</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B17" s="16">
         <v>20</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B18" s="17">
         <v>-0.05</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B19" s="17">
         <v>-0.1</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B20" s="16">
         <v>1.1499999999999999</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B21" s="17">
         <v>0.1</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B22" s="16">
         <v>500</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B23" s="16">
         <v>1.2</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B24" s="17">
         <v>0.15</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B25" s="17">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B26" s="16">
         <v>1.1000000000000001</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B27" s="16">
         <v>7</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B28" s="16">
         <v>20</v>
       </c>
       <c r="C28" s="15" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="18" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -3421,10 +3421,10 @@
         <v>6</v>
       </c>
       <c r="H1" s="19" t="s">
+        <v>245</v>
+      </c>
+      <c r="I1" s="20" t="s">
         <v>246</v>
-      </c>
-      <c r="I1" s="20" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -4256,7 +4256,7 @@
         <v>125</v>
       </c>
       <c r="E1" s="20" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F1" s="24" t="s">
         <v>126</v>
@@ -4757,13 +4757,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="B1" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="C1" s="12" t="s">
         <v>243</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -5045,7 +5045,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="18" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
